--- a/data/trans_camb/IP1011-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP1011-Provincia-trans_camb.xlsx
@@ -583,7 +583,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -739,7 +739,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 1,84</t>
+          <t>-1,98; 1,27</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 0,0</t>
+          <t>-3,84; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 0,0</t>
+          <t>-2,85; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 0,0</t>
+          <t>-2,85; 0,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 0,31</t>
+          <t>-1,59; 0,6</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 0,0</t>
+          <t>-2,0; 0,0</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,59</t>
+          <t>0,0; 3,78</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1363,7 +1363,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,57</t>
+          <t>0,0; 6,75</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,26</t>
+          <t>0,0; 3,63</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1519,7 +1519,7 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1577,7 +1577,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,3</t>
+          <t>0,0; 2,29</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,23</t>
+          <t>0,0; 1,06</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 0,0</t>
+          <t>-1,86; 0,0</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 0,0</t>
+          <t>-1,73; 0,0</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 0,0</t>
+          <t>-3,02; 0,0</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 0,87</t>
+          <t>-2,03; 0,84</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-1,63; -0,19</t>
+          <t>-1,6; -0,19</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 0,26</t>
+          <t>-1,38; 0,24</t>
         </is>
       </c>
     </row>
@@ -1879,12 +1879,12 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 0,41</t>
+          <t>-0,34; 0,42</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 0,0</t>
+          <t>-0,7; 0,0</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -1894,12 +1894,12 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 0,11</t>
+          <t>-0,62; 0,1</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 0,23</t>
+          <t>-0,31; 0,23</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -1975,7 +1975,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-85,29; 330,07</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">

--- a/data/trans_camb/IP1011-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP1011-Provincia-trans_camb.xlsx
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 1,27</t>
+          <t>-1,98; 1,82</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,84; 0,0</t>
+          <t>-3,62; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 0,0</t>
+          <t>-3,09; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 0,0</t>
+          <t>-3,09; 0,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 0,6</t>
+          <t>-1,71; 0,31</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 0,0</t>
+          <t>-2,4; 0,0</t>
         </is>
       </c>
     </row>
@@ -953,7 +953,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,78</t>
+          <t>0,0; 4,43</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,37</t>
+          <t>0,0; 3,04</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,75</t>
+          <t>0,0; 5,54</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,63</t>
+          <t>0,0; 3,31</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1577,7 +1577,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,29</t>
+          <t>0,0; 2,4</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,06</t>
+          <t>0,0; 1,31</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 0,0</t>
+          <t>-2,28; 0,0</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 0,0</t>
+          <t>-2,17; 0,0</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 0,0</t>
+          <t>-2,64; 0,0</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 0,84</t>
+          <t>-2,01; 0,84</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-1,6; -0,19</t>
+          <t>-1,59; -0,19</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 0,24</t>
+          <t>-1,37; 0,26</t>
         </is>
       </c>
     </row>
@@ -1879,32 +1879,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 0,42</t>
+          <t>-0,35; 0,41</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 0,0</t>
+          <t>-0,66; 0,0</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 0,27</t>
+          <t>-0,55; 0,27</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 0,1</t>
+          <t>-0,58; 0,11</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 0,23</t>
+          <t>-0,32; 0,23</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 0,01</t>
+          <t>-0,43; 0,01</t>
         </is>
       </c>
     </row>
@@ -1975,7 +1975,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 331,0</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">

--- a/data/trans_camb/IP1011-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP1011-Provincia-trans_camb.xlsx
@@ -519,13 +519,13 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -749,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-0,61</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-0,61</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>-0,02</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>-0,65</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-0,61</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-0,61</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 1,82</t>
+          <t>-2,93; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 0,0</t>
+          <t>-2,93; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 0,0</t>
+          <t>-2,58; 1,84</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 0,0</t>
+          <t>-3,29; 0,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 0,31</t>
+          <t>-1,89; 0,31</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 0,0</t>
+          <t>-2,2; 0,0</t>
         </is>
       </c>
     </row>
@@ -825,17 +825,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>-3,73%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>0,92</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,92</t>
+          <t>0,0</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -943,7 +943,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 5,59</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,43</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,04</t>
+          <t>0,0; 2,37</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>inf%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>inf%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1373,17 +1373,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
           <t>1,35</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,54</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 7,57</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,31</t>
+          <t>0,0; 3,26</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1449,17 +1449,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>0,46</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1539,7 +1539,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>0,46</t>
+          <t>0,0</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 2,3</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1577,7 +1577,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,4</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,31</t>
+          <t>0,0; 1,23</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>inf%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>inf%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -1685,17 +1685,17 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>-0,79</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
           <t>-0,38</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>-0,38</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>-0,79</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 0,0</t>
+          <t>-2,79; 0,0</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 0,0</t>
+          <t>-1,93; 0,87</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 0,0</t>
+          <t>-1,94; 0,0</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 0,84</t>
+          <t>-1,94; 0,0</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-1,59; -0,19</t>
+          <t>-1,63; -0,19</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 0,26</t>
+          <t>-1,21; 0,26</t>
         </is>
       </c>
     </row>
@@ -1766,17 +1766,17 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
+          <t>-47,44%</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>-47,44%</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -1841,22 +1841,22 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>-0,1</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>-0,18</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
           <t>0,01</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>-0,19</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>-0,1</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>-0,18</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -1879,32 +1879,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 0,41</t>
+          <t>-0,54; 0,27</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 0,0</t>
+          <t>-0,62; 0,11</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 0,27</t>
+          <t>-0,36; 0,41</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 0,11</t>
+          <t>-0,65; 0,0</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 0,23</t>
+          <t>-0,33; 0,23</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 0,01</t>
+          <t>-0,46; 0,01</t>
         </is>
       </c>
     </row>
@@ -1917,22 +1917,22 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>-35,13%</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>-64,88%</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
           <t>7,44%</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>-35,13%</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>-64,88%</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -1975,7 +1975,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 331,0</t>
+          <t>-85,29; 330,07</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
